--- a/data/empresas/[GRUPO] Consolidado Terra Parent/map_pl.xlsx
+++ b/data/empresas/[GRUPO] Consolidado Terra Parent/map_pl.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="626">
   <si>
     <t>N° de cuenta</t>
   </si>
@@ -823,6 +823,54 @@
     <t>3114301</t>
   </si>
   <si>
+    <t>9999300</t>
+  </si>
+  <si>
+    <t>9999305</t>
+  </si>
+  <si>
+    <t>9999310</t>
+  </si>
+  <si>
+    <t>9999315</t>
+  </si>
+  <si>
+    <t>9999320</t>
+  </si>
+  <si>
+    <t>9999325</t>
+  </si>
+  <si>
+    <t>9999330</t>
+  </si>
+  <si>
+    <t>9999335</t>
+  </si>
+  <si>
+    <t>9999340</t>
+  </si>
+  <si>
+    <t>9999345</t>
+  </si>
+  <si>
+    <t>9999350</t>
+  </si>
+  <si>
+    <t>9999355</t>
+  </si>
+  <si>
+    <t>9999360</t>
+  </si>
+  <si>
+    <t>9999365</t>
+  </si>
+  <si>
+    <t>9999370</t>
+  </si>
+  <si>
+    <t>9999375</t>
+  </si>
+  <si>
     <t>FACTURACION CRM</t>
   </si>
   <si>
@@ -1570,12 +1618,66 @@
     <t>IMPUESTO ADICIONAL SOBRE INTERESES BONO 144A (2031)</t>
   </si>
   <si>
+    <t>IMPUESTO UNICO ART 21</t>
+  </si>
+  <si>
     <t>IMPUESTO A LA RENTA (DIFERIDO)</t>
   </si>
   <si>
+    <t>Ajustes consolidacion_INGRESOS DE ARRIENDO FIBRA OPTICA</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_INGRESOS DE ACTIVIDADES ORDINARIAS</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_COSTO DE VENTAS</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_COSTOS DE USO FIBRA OPTICA</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_DEPRECIACION OPERACIONAL</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_OTROS INGRESOS POR FUNCION</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_DEPRECIACIÓN Y AMORTIZACIONES</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_GASTOS DE ADMINISTRACIÓN</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_OTROS EGRESOS POR FUNCIÓN</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_RESULTADO POR INVERSION EN EMPRESAS RELACIONADAS</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_INGRESOS FINANCIEROS</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_INGRESOS FINANCIEROS CON EMPRESAS RELACIONADAS</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_COSTOS FINANCIEROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajustes consolidacion_DIFERENCIAS DE CAMBIO </t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_RESULTADO POR UNIDAD DE REAJUSTE</t>
+  </si>
+  <si>
+    <t>Ajustes consolidacion_GANANCIA (PERDIDA) POR IMPUESTO A LAS GANANCIAS</t>
+  </si>
+  <si>
     <t>Ingresos de arriendo Intercompañia</t>
   </si>
   <si>
+    <t>Uso fibra optica</t>
+  </si>
+  <si>
     <t>Ingresos por servicios domiciliarios</t>
   </si>
   <si>
@@ -1591,6 +1693,9 @@
     <t>Intereses con empresas relacionadas</t>
   </si>
   <si>
+    <t>Ingresos intercompañía</t>
+  </si>
+  <si>
     <t>Costos por servicios de internet, television y telefonía</t>
   </si>
   <si>
@@ -1627,12 +1732,18 @@
     <t>Costos arriendos IC</t>
   </si>
   <si>
+    <t>Costos de uso fibra optica</t>
+  </si>
+  <si>
     <t>Depreciación activos fijos de operación</t>
   </si>
   <si>
     <t>Amortización por derechos de uso</t>
   </si>
   <si>
+    <t>PPA Propiedades planta y equipos</t>
+  </si>
+  <si>
     <t>Servicios básicos y gastos comunes</t>
   </si>
   <si>
@@ -1693,6 +1804,9 @@
     <t>Depreciaciones (2)</t>
   </si>
   <si>
+    <t>Amortizacion cartera clientes</t>
+  </si>
+  <si>
     <t>Venta de activos fijos</t>
   </si>
   <si>
@@ -1705,15 +1819,24 @@
     <t>Diferencia de inventarios</t>
   </si>
   <si>
+    <t>Otros ingresos</t>
+  </si>
+  <si>
     <t>Indemnizaciones y multas</t>
   </si>
   <si>
     <t>Provision obsolescencia</t>
   </si>
   <si>
+    <t>Otros egresos</t>
+  </si>
+  <si>
     <t>Ganancia sobre inversiones en instrumentos financieros</t>
   </si>
   <si>
+    <t>Ingresos por inversiones</t>
+  </si>
+  <si>
     <t>Intereses préstamos bancarios</t>
   </si>
   <si>
@@ -1741,6 +1864,9 @@
     <t>Intereses préstamos empresas relacionadas (2)</t>
   </si>
   <si>
+    <t>Intereses préstamos empresas relacionadas</t>
+  </si>
+  <si>
     <t>Efectivo y efectivo equivalente</t>
   </si>
   <si>
@@ -1763,6 +1889,9 @@
   </si>
   <si>
     <t>Gasto por impuestos diferidos</t>
+  </si>
+  <si>
+    <t>Ajuste impuestos PPA</t>
   </si>
 </sst>
 </file>
@@ -2094,7 +2223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q253"/>
+  <dimension ref="A1:Q269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -2155,10 +2284,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="D2" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2166,10 +2295,10 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="D3" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -2177,10 +2306,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -2188,10 +2317,10 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -2199,10 +2328,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="D6" t="s">
-        <v>521</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -2210,10 +2339,10 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="D7" t="s">
-        <v>521</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2221,10 +2350,10 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="D8" t="s">
-        <v>521</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -2232,10 +2361,10 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="D9" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -2243,10 +2372,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="D10" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -2254,13 +2383,13 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="D11" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
       <c r="H11" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -2268,10 +2397,10 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="D12" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -2279,10 +2408,10 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="D13" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -2290,10 +2419,10 @@
         <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="D14" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -2301,10 +2430,10 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="D15" t="s">
-        <v>523</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -2312,10 +2441,10 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="D16" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2323,10 +2452,10 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="D17" t="s">
-        <v>523</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2334,10 +2463,10 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>523</v>
+        <v>557</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2345,13 +2474,13 @@
         <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="E19" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H19" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2359,10 +2488,10 @@
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="E20" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -2370,10 +2499,10 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="E21" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2381,13 +2510,13 @@
         <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="E22" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H22" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2395,13 +2524,13 @@
         <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="E23" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H23" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2409,13 +2538,13 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="E24" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H24" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2423,10 +2552,10 @@
         <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="E25" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2434,10 +2563,10 @@
         <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="E26" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2445,10 +2574,10 @@
         <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="E27" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2456,10 +2585,10 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E28" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2467,10 +2596,10 @@
         <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="E29" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2478,10 +2607,10 @@
         <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="E30" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2489,13 +2618,13 @@
         <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="E31" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H31" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2503,10 +2632,10 @@
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="J32" t="s">
-        <v>559</v>
+        <v>597</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2514,10 +2643,10 @@
         <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="J33" t="s">
-        <v>560</v>
+        <v>598</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2525,10 +2654,10 @@
         <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="L34" t="s">
-        <v>565</v>
+        <v>605</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2536,10 +2665,10 @@
         <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="J35" t="s">
-        <v>561</v>
+        <v>599</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2547,10 +2676,10 @@
         <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="C36" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2558,10 +2687,10 @@
         <v>52</v>
       </c>
       <c r="B37" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E37" t="s">
-        <v>527</v>
+        <v>562</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2569,10 +2698,10 @@
         <v>53</v>
       </c>
       <c r="B38" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="H38" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2580,13 +2709,13 @@
         <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="E39" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H39" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2594,13 +2723,13 @@
         <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="E40" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H40" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2608,13 +2737,13 @@
         <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="E41" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H41" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2622,13 +2751,13 @@
         <v>57</v>
       </c>
       <c r="B42" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E42" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H42" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2636,13 +2765,13 @@
         <v>58</v>
       </c>
       <c r="B43" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E43" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H43" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2650,13 +2779,13 @@
         <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="E44" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H44" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2664,13 +2793,13 @@
         <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="E45" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H45" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2678,13 +2807,13 @@
         <v>61</v>
       </c>
       <c r="B46" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E46" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H46" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2692,13 +2821,13 @@
         <v>62</v>
       </c>
       <c r="B47" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="E47" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H47" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2706,13 +2835,13 @@
         <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E48" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H48" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2720,13 +2849,13 @@
         <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="E49" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H49" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2734,13 +2863,13 @@
         <v>65</v>
       </c>
       <c r="B50" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="E50" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H50" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2748,13 +2877,13 @@
         <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E51" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H51" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2762,16 +2891,16 @@
         <v>67</v>
       </c>
       <c r="B52" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="E52" t="s">
-        <v>529</v>
+        <v>564</v>
       </c>
       <c r="H52" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="K52" t="s">
-        <v>563</v>
+        <v>602</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2779,13 +2908,13 @@
         <v>68</v>
       </c>
       <c r="B53" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="E53" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H53" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2793,13 +2922,13 @@
         <v>69</v>
       </c>
       <c r="B54" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="E54" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H54" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2807,13 +2936,13 @@
         <v>70</v>
       </c>
       <c r="B55" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="E55" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H55" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2821,13 +2950,13 @@
         <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="E56" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H56" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2835,13 +2964,13 @@
         <v>72</v>
       </c>
       <c r="B57" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="E57" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H57" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2849,13 +2978,13 @@
         <v>73</v>
       </c>
       <c r="B58" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="E58" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H58" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2863,13 +2992,13 @@
         <v>74</v>
       </c>
       <c r="B59" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="E59" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H59" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2877,13 +3006,13 @@
         <v>75</v>
       </c>
       <c r="B60" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="E60" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H60" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2891,13 +3020,13 @@
         <v>76</v>
       </c>
       <c r="B61" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="E61" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H61" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2905,13 +3034,13 @@
         <v>77</v>
       </c>
       <c r="B62" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="E62" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H62" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2919,13 +3048,13 @@
         <v>78</v>
       </c>
       <c r="B63" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="E63" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H63" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -2933,13 +3062,13 @@
         <v>79</v>
       </c>
       <c r="B64" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="E64" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H64" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2947,13 +3076,13 @@
         <v>80</v>
       </c>
       <c r="B65" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="E65" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H65" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2961,13 +3090,13 @@
         <v>81</v>
       </c>
       <c r="B66" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="E66" t="s">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="H66" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2975,13 +3104,13 @@
         <v>82</v>
       </c>
       <c r="B67" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E67" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H67" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2989,13 +3118,13 @@
         <v>83</v>
       </c>
       <c r="B68" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="E68" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H68" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -3003,10 +3132,10 @@
         <v>84</v>
       </c>
       <c r="B69" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="H69" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -3014,13 +3143,13 @@
         <v>85</v>
       </c>
       <c r="B70" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="E70" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H70" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3028,13 +3157,13 @@
         <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="E71" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H71" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3042,13 +3171,13 @@
         <v>87</v>
       </c>
       <c r="B72" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="E72" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H72" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3056,13 +3185,13 @@
         <v>88</v>
       </c>
       <c r="B73" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="E73" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="H73" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3070,13 +3199,13 @@
         <v>89</v>
       </c>
       <c r="B74" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E74" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H74" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3084,13 +3213,13 @@
         <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="E75" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H75" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3098,13 +3227,13 @@
         <v>91</v>
       </c>
       <c r="B76" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="E76" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H76" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3112,10 +3241,10 @@
         <v>92</v>
       </c>
       <c r="B77" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="H77" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3123,13 +3252,13 @@
         <v>93</v>
       </c>
       <c r="B78" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="E78" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H78" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3137,13 +3266,13 @@
         <v>94</v>
       </c>
       <c r="B79" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="E79" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H79" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3151,13 +3280,13 @@
         <v>95</v>
       </c>
       <c r="B80" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="E80" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="H80" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3165,10 +3294,10 @@
         <v>96</v>
       </c>
       <c r="B81" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="E81" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3176,10 +3305,10 @@
         <v>97</v>
       </c>
       <c r="B82" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="E82" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3187,10 +3316,10 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="F83" t="s">
-        <v>536</v>
+        <v>571</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3198,10 +3327,10 @@
         <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="H84" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3209,13 +3338,13 @@
         <v>100</v>
       </c>
       <c r="B85" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="E85" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H85" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3223,13 +3352,13 @@
         <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="E86" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H86" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3237,13 +3366,13 @@
         <v>102</v>
       </c>
       <c r="B87" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="E87" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H87" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3251,13 +3380,13 @@
         <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="E88" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H88" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3265,13 +3394,13 @@
         <v>104</v>
       </c>
       <c r="B89" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="E89" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H89" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3279,13 +3408,13 @@
         <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="E90" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H90" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3293,13 +3422,13 @@
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="E91" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H91" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3307,13 +3436,13 @@
         <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="E92" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H92" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -3321,13 +3450,13 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="E93" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H93" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -3335,13 +3464,13 @@
         <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="E94" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H94" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -3349,16 +3478,16 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="E95" t="s">
-        <v>529</v>
+        <v>564</v>
       </c>
       <c r="H95" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="K95" t="s">
-        <v>563</v>
+        <v>602</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -3366,13 +3495,13 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="E96" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H96" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3380,13 +3509,13 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="H97" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="M97" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3394,7 +3523,7 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3402,13 +3531,13 @@
         <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="E99" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H99" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3416,13 +3545,13 @@
         <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="E100" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H100" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3430,13 +3559,13 @@
         <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="E101" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H101" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3444,13 +3573,13 @@
         <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="E102" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H102" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3458,13 +3587,13 @@
         <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="E103" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H103" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3472,13 +3601,13 @@
         <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="E104" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H104" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3486,13 +3615,13 @@
         <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="E105" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H105" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3500,13 +3629,13 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="E106" t="s">
-        <v>534</v>
+        <v>569</v>
       </c>
       <c r="K106" t="s">
-        <v>564</v>
+        <v>603</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3514,16 +3643,16 @@
         <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="E107" t="s">
-        <v>534</v>
+        <v>569</v>
       </c>
       <c r="H107" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="J107" t="s">
-        <v>562</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3531,13 +3660,13 @@
         <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="G108" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I108" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3545,10 +3674,10 @@
         <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="I109" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3556,13 +3685,13 @@
         <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="G110" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I110" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3570,10 +3699,10 @@
         <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="M111" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3581,13 +3710,13 @@
         <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="G112" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I112" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -3595,13 +3724,13 @@
         <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="G113" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I113" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -3609,13 +3738,13 @@
         <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="G114" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I114" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3623,13 +3752,13 @@
         <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="G115" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I115" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3637,13 +3766,13 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="G116" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I116" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3651,13 +3780,13 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="G117" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I117" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -3665,13 +3794,13 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="G118" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I118" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -3679,13 +3808,13 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="G119" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I119" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3693,13 +3822,13 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="G120" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I120" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3707,13 +3836,13 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="G121" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I121" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -3721,13 +3850,13 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="G122" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I122" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -3735,13 +3864,13 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="G123" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I123" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -3749,13 +3878,13 @@
         <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="G124" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I124" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -3763,13 +3892,13 @@
         <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="G125" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I125" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -3777,13 +3906,13 @@
         <v>141</v>
       </c>
       <c r="B126" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="G126" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="I126" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -3791,13 +3920,13 @@
         <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="E127" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H127" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -3805,13 +3934,13 @@
         <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="E128" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H128" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -3819,13 +3948,13 @@
         <v>144</v>
       </c>
       <c r="B129" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="E129" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H129" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -3833,13 +3962,13 @@
         <v>145</v>
       </c>
       <c r="B130" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="E130" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H130" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -3847,13 +3976,13 @@
         <v>146</v>
       </c>
       <c r="B131" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="E131" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H131" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -3861,16 +3990,16 @@
         <v>147</v>
       </c>
       <c r="B132" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="E132" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H132" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="M132" t="s">
-        <v>567</v>
+        <v>608</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -3878,13 +4007,13 @@
         <v>148</v>
       </c>
       <c r="B133" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="E133" t="s">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="H133" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -3892,13 +4021,13 @@
         <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="E134" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H134" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -3906,13 +4035,13 @@
         <v>150</v>
       </c>
       <c r="B135" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="E135" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H135" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -3920,13 +4049,13 @@
         <v>151</v>
       </c>
       <c r="B136" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="E136" t="s">
-        <v>534</v>
+        <v>569</v>
       </c>
       <c r="H136" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -3934,13 +4063,13 @@
         <v>152</v>
       </c>
       <c r="B137" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="E137" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H137" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -3948,13 +4077,13 @@
         <v>153</v>
       </c>
       <c r="B138" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="E138" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H138" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -3962,13 +4091,13 @@
         <v>154</v>
       </c>
       <c r="B139" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="E139" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H139" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -3976,13 +4105,13 @@
         <v>155</v>
       </c>
       <c r="B140" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="E140" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H140" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -3990,13 +4119,13 @@
         <v>156</v>
       </c>
       <c r="B141" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="E141" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H141" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4004,13 +4133,13 @@
         <v>157</v>
       </c>
       <c r="B142" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="E142" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H142" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4018,13 +4147,13 @@
         <v>158</v>
       </c>
       <c r="B143" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E143" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H143" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4032,13 +4161,13 @@
         <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="E144" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H144" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4046,13 +4175,13 @@
         <v>160</v>
       </c>
       <c r="B145" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="E145" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H145" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4060,13 +4189,13 @@
         <v>161</v>
       </c>
       <c r="B146" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="E146" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H146" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4074,13 +4203,13 @@
         <v>162</v>
       </c>
       <c r="B147" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="E147" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H147" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4088,13 +4217,13 @@
         <v>163</v>
       </c>
       <c r="B148" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="E148" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H148" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4102,13 +4231,13 @@
         <v>164</v>
       </c>
       <c r="B149" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="E149" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H149" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4116,13 +4245,13 @@
         <v>165</v>
       </c>
       <c r="B150" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="E150" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H150" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4130,10 +4259,10 @@
         <v>166</v>
       </c>
       <c r="B151" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="H151" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4141,13 +4270,13 @@
         <v>167</v>
       </c>
       <c r="B152" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="E152" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="H152" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4155,10 +4284,10 @@
         <v>168</v>
       </c>
       <c r="B153" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="M153" t="s">
-        <v>568</v>
+        <v>609</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -4166,13 +4295,13 @@
         <v>169</v>
       </c>
       <c r="B154" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="G154" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
       <c r="I154" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -4180,13 +4309,13 @@
         <v>170</v>
       </c>
       <c r="B155" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G155" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
       <c r="I155" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -4194,10 +4323,10 @@
         <v>171</v>
       </c>
       <c r="B156" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="E156" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -4205,13 +4334,13 @@
         <v>172</v>
       </c>
       <c r="B157" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="G157" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
       <c r="I157" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -4219,10 +4348,10 @@
         <v>173</v>
       </c>
       <c r="B158" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="M158" t="s">
-        <v>568</v>
+        <v>609</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -4230,10 +4359,10 @@
         <v>174</v>
       </c>
       <c r="B159" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="M159" t="s">
-        <v>568</v>
+        <v>609</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -4241,13 +4370,13 @@
         <v>175</v>
       </c>
       <c r="B160" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="E160" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H160" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -4255,13 +4384,13 @@
         <v>176</v>
       </c>
       <c r="B161" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="E161" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H161" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -4269,13 +4398,13 @@
         <v>177</v>
       </c>
       <c r="B162" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="E162" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H162" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -4283,13 +4412,13 @@
         <v>178</v>
       </c>
       <c r="B163" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="E163" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H163" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -4297,13 +4426,13 @@
         <v>179</v>
       </c>
       <c r="B164" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="E164" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H164" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -4311,13 +4440,13 @@
         <v>180</v>
       </c>
       <c r="B165" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="E165" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H165" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -4325,13 +4454,13 @@
         <v>181</v>
       </c>
       <c r="B166" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="E166" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H166" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -4339,13 +4468,13 @@
         <v>182</v>
       </c>
       <c r="B167" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="E167" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H167" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -4353,13 +4482,13 @@
         <v>183</v>
       </c>
       <c r="B168" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="E168" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H168" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -4367,13 +4496,13 @@
         <v>184</v>
       </c>
       <c r="B169" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="E169" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="H169" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -4381,10 +4510,10 @@
         <v>185</v>
       </c>
       <c r="B170" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="H170" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -4392,10 +4521,10 @@
         <v>186</v>
       </c>
       <c r="B171" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="E171" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -4403,13 +4532,13 @@
         <v>187</v>
       </c>
       <c r="B172" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="E172" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="H172" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -4417,10 +4546,10 @@
         <v>188</v>
       </c>
       <c r="B173" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="K173" t="s">
-        <v>561</v>
+        <v>599</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -4428,13 +4557,13 @@
         <v>189</v>
       </c>
       <c r="B174" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="E174" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="K174" t="s">
-        <v>564</v>
+        <v>603</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -4442,10 +4571,10 @@
         <v>190</v>
       </c>
       <c r="B175" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="E175" t="s">
-        <v>527</v>
+        <v>562</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -4453,10 +4582,10 @@
         <v>191</v>
       </c>
       <c r="B176" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="E176" t="s">
-        <v>534</v>
+        <v>569</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -4464,7 +4593,7 @@
         <v>192</v>
       </c>
       <c r="B177" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -4472,10 +4601,10 @@
         <v>193</v>
       </c>
       <c r="B178" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="D178" t="s">
-        <v>524</v>
+        <v>558</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -4483,10 +4612,10 @@
         <v>194</v>
       </c>
       <c r="B179" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="M179" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -4494,10 +4623,10 @@
         <v>195</v>
       </c>
       <c r="B180" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="M180" t="s">
-        <v>569</v>
+        <v>610</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -4505,10 +4634,10 @@
         <v>196</v>
       </c>
       <c r="B181" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="M181" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -4516,10 +4645,10 @@
         <v>197</v>
       </c>
       <c r="B182" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="M182" t="s">
-        <v>570</v>
+        <v>611</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -4527,10 +4656,10 @@
         <v>198</v>
       </c>
       <c r="B183" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="M183" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -4538,10 +4667,10 @@
         <v>199</v>
       </c>
       <c r="B184" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="M184" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -4549,10 +4678,10 @@
         <v>200</v>
       </c>
       <c r="B185" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="M185" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -4560,16 +4689,16 @@
         <v>201</v>
       </c>
       <c r="B186" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="E186" t="s">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="H186" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="M186" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -4577,10 +4706,10 @@
         <v>202</v>
       </c>
       <c r="B187" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="M187" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -4588,10 +4717,10 @@
         <v>203</v>
       </c>
       <c r="B188" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="M188" t="s">
-        <v>571</v>
+        <v>612</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -4599,10 +4728,10 @@
         <v>204</v>
       </c>
       <c r="B189" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="M189" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -4610,10 +4739,10 @@
         <v>205</v>
       </c>
       <c r="B190" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="M190" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -4621,10 +4750,10 @@
         <v>206</v>
       </c>
       <c r="B191" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="M191" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -4632,10 +4761,10 @@
         <v>207</v>
       </c>
       <c r="B192" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="M192" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -4643,10 +4772,10 @@
         <v>208</v>
       </c>
       <c r="B193" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="M193" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -4654,10 +4783,10 @@
         <v>209</v>
       </c>
       <c r="B194" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="M194" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -4665,10 +4794,10 @@
         <v>210</v>
       </c>
       <c r="B195" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="M195" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -4676,10 +4805,10 @@
         <v>211</v>
       </c>
       <c r="B196" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="M196" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -4687,10 +4816,10 @@
         <v>212</v>
       </c>
       <c r="B197" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="M197" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -4698,10 +4827,10 @@
         <v>213</v>
       </c>
       <c r="B198" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="M198" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -4709,10 +4838,10 @@
         <v>214</v>
       </c>
       <c r="B199" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="M199" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -4720,10 +4849,10 @@
         <v>215</v>
       </c>
       <c r="B200" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="M200" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -4731,10 +4860,10 @@
         <v>216</v>
       </c>
       <c r="B201" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="M201" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -4742,10 +4871,10 @@
         <v>217</v>
       </c>
       <c r="B202" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="M202" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -4753,10 +4882,10 @@
         <v>218</v>
       </c>
       <c r="B203" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="M203" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -4764,10 +4893,10 @@
         <v>219</v>
       </c>
       <c r="B204" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="M204" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -4775,10 +4904,10 @@
         <v>220</v>
       </c>
       <c r="B205" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="M205" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -4786,10 +4915,10 @@
         <v>221</v>
       </c>
       <c r="B206" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="M206" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -4797,10 +4926,10 @@
         <v>222</v>
       </c>
       <c r="B207" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="M207" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -4808,10 +4937,10 @@
         <v>223</v>
       </c>
       <c r="B208" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="M208" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -4819,10 +4948,10 @@
         <v>224</v>
       </c>
       <c r="B209" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="M209" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -4830,10 +4959,10 @@
         <v>225</v>
       </c>
       <c r="B210" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="M210" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -4841,10 +4970,10 @@
         <v>226</v>
       </c>
       <c r="B211" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="M211" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -4852,10 +4981,10 @@
         <v>227</v>
       </c>
       <c r="B212" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="M212" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -4863,10 +4992,10 @@
         <v>228</v>
       </c>
       <c r="B213" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="M213" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -4874,10 +5003,10 @@
         <v>229</v>
       </c>
       <c r="B214" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="M214" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -4885,10 +5014,10 @@
         <v>230</v>
       </c>
       <c r="B215" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="M215" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -4896,10 +5025,10 @@
         <v>231</v>
       </c>
       <c r="B216" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="M216" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -4907,10 +5036,10 @@
         <v>232</v>
       </c>
       <c r="B217" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="M217" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -4918,10 +5047,10 @@
         <v>233</v>
       </c>
       <c r="B218" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="M218" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -4929,10 +5058,10 @@
         <v>234</v>
       </c>
       <c r="B219" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="M219" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -4940,10 +5069,10 @@
         <v>235</v>
       </c>
       <c r="B220" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="M220" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -4951,10 +5080,10 @@
         <v>236</v>
       </c>
       <c r="B221" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="M221" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -4962,10 +5091,10 @@
         <v>237</v>
       </c>
       <c r="B222" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="M222" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="223" spans="1:13">
@@ -4973,10 +5102,10 @@
         <v>238</v>
       </c>
       <c r="B223" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="M223" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -4984,10 +5113,10 @@
         <v>239</v>
       </c>
       <c r="B224" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="M224" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="225" spans="1:14">
@@ -4995,10 +5124,10 @@
         <v>240</v>
       </c>
       <c r="B225" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="M225" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
     </row>
     <row r="226" spans="1:14">
@@ -5006,10 +5135,10 @@
         <v>241</v>
       </c>
       <c r="B226" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="M226" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
     </row>
     <row r="227" spans="1:14">
@@ -5017,10 +5146,10 @@
         <v>242</v>
       </c>
       <c r="B227" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="M227" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
     </row>
     <row r="228" spans="1:14">
@@ -5028,10 +5157,10 @@
         <v>243</v>
       </c>
       <c r="B228" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="M228" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="229" spans="1:14">
@@ -5039,10 +5168,10 @@
         <v>244</v>
       </c>
       <c r="B229" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="M229" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
     </row>
     <row r="230" spans="1:14">
@@ -5050,10 +5179,10 @@
         <v>245</v>
       </c>
       <c r="B230" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="M230" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="231" spans="1:14">
@@ -5061,7 +5190,7 @@
         <v>246</v>
       </c>
       <c r="B231" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
     </row>
     <row r="232" spans="1:14">
@@ -5069,10 +5198,10 @@
         <v>247</v>
       </c>
       <c r="B232" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="N232" t="s">
-        <v>575</v>
+        <v>617</v>
       </c>
     </row>
     <row r="233" spans="1:14">
@@ -5080,10 +5209,10 @@
         <v>248</v>
       </c>
       <c r="B233" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="N233" t="s">
-        <v>576</v>
+        <v>618</v>
       </c>
     </row>
     <row r="234" spans="1:14">
@@ -5091,10 +5220,10 @@
         <v>249</v>
       </c>
       <c r="B234" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="N234" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="235" spans="1:14">
@@ -5102,10 +5231,10 @@
         <v>250</v>
       </c>
       <c r="B235" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="N235" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="236" spans="1:14">
@@ -5113,10 +5242,10 @@
         <v>251</v>
       </c>
       <c r="B236" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="N236" t="s">
-        <v>578</v>
+        <v>620</v>
       </c>
     </row>
     <row r="237" spans="1:14">
@@ -5124,10 +5253,10 @@
         <v>252</v>
       </c>
       <c r="B237" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="N237" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="238" spans="1:14">
@@ -5135,10 +5264,10 @@
         <v>253</v>
       </c>
       <c r="B238" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="N238" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="239" spans="1:14">
@@ -5146,10 +5275,10 @@
         <v>254</v>
       </c>
       <c r="B239" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="N239" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="240" spans="1:14">
@@ -5157,10 +5286,10 @@
         <v>255</v>
       </c>
       <c r="B240" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="N240" t="s">
-        <v>576</v>
+        <v>618</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -5168,10 +5297,10 @@
         <v>256</v>
       </c>
       <c r="B241" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="N241" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -5179,10 +5308,10 @@
         <v>257</v>
       </c>
       <c r="B242" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="N242" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -5190,10 +5319,10 @@
         <v>258</v>
       </c>
       <c r="B243" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="N243" t="s">
-        <v>578</v>
+        <v>620</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -5201,10 +5330,10 @@
         <v>259</v>
       </c>
       <c r="B244" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="N244" t="s">
-        <v>579</v>
+        <v>621</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -5212,10 +5341,10 @@
         <v>260</v>
       </c>
       <c r="B245" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="N245" t="s">
-        <v>578</v>
+        <v>620</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -5223,10 +5352,10 @@
         <v>261</v>
       </c>
       <c r="B246" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="N246" t="s">
-        <v>578</v>
+        <v>620</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -5234,10 +5363,10 @@
         <v>262</v>
       </c>
       <c r="B247" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="O247" t="s">
-        <v>580</v>
+        <v>622</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -5245,10 +5374,10 @@
         <v>263</v>
       </c>
       <c r="B248" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="N248" t="s">
-        <v>577</v>
+        <v>619</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -5256,10 +5385,10 @@
         <v>264</v>
       </c>
       <c r="B249" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="O249" t="s">
-        <v>561</v>
+        <v>599</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -5267,10 +5396,10 @@
         <v>265</v>
       </c>
       <c r="B250" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P250" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -5278,10 +5407,10 @@
         <v>266</v>
       </c>
       <c r="B251" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="M251" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -5289,10 +5418,10 @@
         <v>267</v>
       </c>
       <c r="B252" t="s">
-        <v>267</v>
+        <v>534</v>
       </c>
       <c r="P252" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -5300,10 +5429,177 @@
         <v>268</v>
       </c>
       <c r="B253" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="P253" t="s">
-        <v>582</v>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16">
+      <c r="A254" t="s">
+        <v>269</v>
+      </c>
+      <c r="B254" t="s">
+        <v>536</v>
+      </c>
+      <c r="C254" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16">
+      <c r="A255" t="s">
+        <v>270</v>
+      </c>
+      <c r="B255" t="s">
+        <v>537</v>
+      </c>
+      <c r="D255" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16">
+      <c r="A256" t="s">
+        <v>271</v>
+      </c>
+      <c r="B256" t="s">
+        <v>538</v>
+      </c>
+      <c r="E256" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="257" spans="1:17">
+      <c r="A257" t="s">
+        <v>272</v>
+      </c>
+      <c r="B257" t="s">
+        <v>539</v>
+      </c>
+      <c r="F257" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="258" spans="1:17">
+      <c r="A258" t="s">
+        <v>273</v>
+      </c>
+      <c r="B258" t="s">
+        <v>540</v>
+      </c>
+      <c r="G258" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17">
+      <c r="A259" t="s">
+        <v>274</v>
+      </c>
+      <c r="B259" t="s">
+        <v>541</v>
+      </c>
+      <c r="J259" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17">
+      <c r="A260" t="s">
+        <v>275</v>
+      </c>
+      <c r="B260" t="s">
+        <v>542</v>
+      </c>
+      <c r="I260" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17">
+      <c r="A261" t="s">
+        <v>276</v>
+      </c>
+      <c r="B261" t="s">
+        <v>543</v>
+      </c>
+      <c r="H261" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="262" spans="1:17">
+      <c r="A262" t="s">
+        <v>277</v>
+      </c>
+      <c r="B262" t="s">
+        <v>544</v>
+      </c>
+      <c r="K262" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17">
+      <c r="A263" t="s">
+        <v>278</v>
+      </c>
+      <c r="B263" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="264" spans="1:17">
+      <c r="A264" t="s">
+        <v>279</v>
+      </c>
+      <c r="B264" t="s">
+        <v>546</v>
+      </c>
+      <c r="L264" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17">
+      <c r="A265" t="s">
+        <v>280</v>
+      </c>
+      <c r="B265" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="266" spans="1:17">
+      <c r="A266" t="s">
+        <v>281</v>
+      </c>
+      <c r="B266" t="s">
+        <v>548</v>
+      </c>
+      <c r="M266" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="267" spans="1:17">
+      <c r="A267" t="s">
+        <v>282</v>
+      </c>
+      <c r="B267" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="268" spans="1:17">
+      <c r="A268" t="s">
+        <v>283</v>
+      </c>
+      <c r="B268" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="269" spans="1:17">
+      <c r="A269" t="s">
+        <v>284</v>
+      </c>
+      <c r="B269" t="s">
+        <v>551</v>
+      </c>
+      <c r="P269" t="s">
+        <v>625</v>
       </c>
     </row>
   </sheetData>
